--- a/v6/files/r-interview-notes.xlsx
+++ b/v6/files/r-interview-notes.xlsx
@@ -499,7 +499,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>5. Когда три разговора подряд без нового, картина сложилась. Сводка считает это сама.</t>
+          <t>5. Когда три разговора подряд без нового, картина сложилась. Сводка показывает, сколько всего разговоров без нового; три подряд проверьте по последним строкам листа «Интервью».</t>
         </is>
       </c>
     </row>
